--- a/feedback_forms/047_municipality_citizen_input_information_collection_form--feedback_forms.xlsx
+++ b/feedback_forms/047_municipality_citizen_input_information_collection_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_0}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 0}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'mayor',_'value':_1}</t>
+          <t>mayor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Mayor', 'value': 1}</t>
+          <t>Mayor</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'department_1',_'value':_2}</t>
+          <t>department_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Department 1', 'value': 2}</t>
+          <t>Department 1</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'department_2',_'value':_3}</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Department 2', 'value': 3}</t>
+          <t>Department 2</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'very_good',_'value':_5}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good', 'value': 5}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_4}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 4}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'bad',_'value':_2}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Bad', 'value': 2}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_bad',_'value':_1}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very Bad', 'value': 1}</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
